--- a/storage/templates/Manolete.xlsx
+++ b/storage/templates/Manolete.xlsx
@@ -305,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -409,6 +409,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -739,7 +742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN109"/>
+  <dimension ref="A1:AN114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="25.05" customHeight="1"/>
   <cols>
     <col width="10.77734375" customWidth="1" style="7" min="1" max="1"/>
@@ -6085,220 +6088,369 @@
       </c>
     </row>
     <row r="79" ht="25.05" customHeight="1">
-      <c r="C79" s="15">
-        <f>SUM(C7:C78)</f>
-        <v/>
-      </c>
-      <c r="E79" s="22" t="inlineStr">
+      <c r="A79" s="36" t="inlineStr">
+        <is>
+          <t>8983</t>
+        </is>
+      </c>
+      <c r="B79" s="36" t="inlineStr">
+        <is>
+          <t>CAVA CASTELL D'ORDAL BRUT 75 CL</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="37" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F79" s="25">
+        <f>C79*E79</f>
+        <v/>
+      </c>
+      <c r="G79" s="18" t="n"/>
+      <c r="H79" s="18" t="n"/>
+      <c r="I79" s="18" t="n"/>
+      <c r="J79" s="18" t="n"/>
+      <c r="K79" s="18" t="n"/>
+      <c r="L79" s="18" t="n"/>
+      <c r="M79" s="18" t="n"/>
+      <c r="N79" s="18" t="n"/>
+      <c r="O79" s="18" t="n"/>
+      <c r="P79" s="18" t="n"/>
+      <c r="Q79" s="18" t="n"/>
+      <c r="R79" s="18" t="n"/>
+      <c r="S79" s="18" t="n"/>
+      <c r="T79" s="18" t="n"/>
+      <c r="U79" s="18" t="n"/>
+      <c r="V79" s="18" t="n"/>
+      <c r="W79" s="18" t="n"/>
+      <c r="X79" s="18" t="n"/>
+      <c r="Y79" s="18" t="n"/>
+      <c r="Z79" s="18" t="n"/>
+      <c r="AA79" s="18" t="n"/>
+      <c r="AB79" s="18" t="n"/>
+      <c r="AC79" s="18" t="n"/>
+      <c r="AD79" s="18" t="n"/>
+      <c r="AE79" s="18" t="n"/>
+      <c r="AF79" s="18" t="n"/>
+      <c r="AG79" s="18" t="n"/>
+      <c r="AH79" s="18" t="n"/>
+      <c r="AI79" s="18" t="n"/>
+      <c r="AJ79" s="18" t="n"/>
+      <c r="AK79" s="18" t="n"/>
+      <c r="AL79" s="19">
+        <f>SUM(G79:AK79)</f>
+        <v/>
+      </c>
+      <c r="AM79" s="20">
+        <f>SUM(C79,AL79)</f>
+        <v/>
+      </c>
+      <c r="AN79" s="21">
+        <f>E79*AM79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="25.05" customHeight="1">
+      <c r="A80" s="36" t="inlineStr">
+        <is>
+          <t>28869</t>
+        </is>
+      </c>
+      <c r="B80" s="36" t="inlineStr">
+        <is>
+          <t>VINO TTO MALPASTOR CRIANZA 75 CL</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="37" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F80" s="25">
+        <f>C80*E80</f>
+        <v/>
+      </c>
+      <c r="G80" s="18" t="n"/>
+      <c r="H80" s="18" t="n"/>
+      <c r="I80" s="18" t="n"/>
+      <c r="J80" s="18" t="n"/>
+      <c r="K80" s="18" t="n"/>
+      <c r="L80" s="18" t="n"/>
+      <c r="M80" s="18" t="n"/>
+      <c r="N80" s="18" t="n"/>
+      <c r="O80" s="18" t="n"/>
+      <c r="P80" s="18" t="n"/>
+      <c r="Q80" s="18" t="n"/>
+      <c r="R80" s="18" t="n"/>
+      <c r="S80" s="18" t="n"/>
+      <c r="T80" s="18" t="n"/>
+      <c r="U80" s="18" t="n"/>
+      <c r="V80" s="18" t="n"/>
+      <c r="W80" s="18" t="n"/>
+      <c r="X80" s="18" t="n"/>
+      <c r="Y80" s="18" t="n"/>
+      <c r="Z80" s="18" t="n"/>
+      <c r="AA80" s="18" t="n"/>
+      <c r="AB80" s="18" t="n"/>
+      <c r="AC80" s="18" t="n"/>
+      <c r="AD80" s="18" t="n"/>
+      <c r="AE80" s="18" t="n"/>
+      <c r="AF80" s="18" t="n"/>
+      <c r="AG80" s="18" t="n"/>
+      <c r="AH80" s="18" t="n"/>
+      <c r="AI80" s="18" t="n"/>
+      <c r="AJ80" s="18" t="n"/>
+      <c r="AK80" s="18" t="n"/>
+      <c r="AL80" s="19">
+        <f>SUM(G80:AK80)</f>
+        <v/>
+      </c>
+      <c r="AM80" s="20">
+        <f>SUM(C80,AL80)</f>
+        <v/>
+      </c>
+      <c r="AN80" s="21">
+        <f>E80*AM80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="25.05" customHeight="1">
+      <c r="A81" s="36" t="inlineStr">
+        <is>
+          <t>4098</t>
+        </is>
+      </c>
+      <c r="B81" s="36" t="inlineStr">
+        <is>
+          <t>REFRESCO BIB TONICA NORDIC MIST</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="37" t="inlineStr">
+        <is>
+          <t>LITRO</t>
+        </is>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>7.68074</v>
+      </c>
+      <c r="F81" s="25">
+        <f>C81*E81</f>
+        <v/>
+      </c>
+      <c r="G81" s="18" t="n"/>
+      <c r="H81" s="18" t="n"/>
+      <c r="I81" s="18" t="n"/>
+      <c r="J81" s="18" t="n"/>
+      <c r="K81" s="18" t="n"/>
+      <c r="L81" s="18" t="n"/>
+      <c r="M81" s="18" t="n"/>
+      <c r="N81" s="18" t="n"/>
+      <c r="O81" s="18" t="n"/>
+      <c r="P81" s="18" t="n"/>
+      <c r="Q81" s="18" t="n"/>
+      <c r="R81" s="18" t="n"/>
+      <c r="S81" s="18" t="n"/>
+      <c r="T81" s="18" t="n"/>
+      <c r="U81" s="18" t="n"/>
+      <c r="V81" s="18" t="n"/>
+      <c r="W81" s="18" t="n"/>
+      <c r="X81" s="18" t="n"/>
+      <c r="Y81" s="18" t="n"/>
+      <c r="Z81" s="18" t="n"/>
+      <c r="AA81" s="18" t="n"/>
+      <c r="AB81" s="18" t="n"/>
+      <c r="AC81" s="18" t="n"/>
+      <c r="AD81" s="18" t="n"/>
+      <c r="AE81" s="18" t="n"/>
+      <c r="AF81" s="18" t="n"/>
+      <c r="AG81" s="18" t="n"/>
+      <c r="AH81" s="18" t="n"/>
+      <c r="AI81" s="18" t="n"/>
+      <c r="AJ81" s="18" t="n"/>
+      <c r="AK81" s="18" t="n"/>
+      <c r="AL81" s="19">
+        <f>SUM(G81:AK81)</f>
+        <v/>
+      </c>
+      <c r="AM81" s="20">
+        <f>SUM(C81,AL81)</f>
+        <v/>
+      </c>
+      <c r="AN81" s="21">
+        <f>E81*AM81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="25.05" customHeight="1">
+      <c r="A82" s="36" t="inlineStr">
+        <is>
+          <t>19982</t>
+        </is>
+      </c>
+      <c r="B82" s="36" t="inlineStr">
+        <is>
+          <t>SERVILLETA CANGURO S/LOGO 40X40 CM 50 UDS</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="37" t="inlineStr">
+        <is>
+          <t>PAQUETE</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>5.5134</v>
+      </c>
+      <c r="F82" s="25">
+        <f>C82*E82</f>
+        <v/>
+      </c>
+      <c r="G82" s="18" t="n"/>
+      <c r="H82" s="18" t="n"/>
+      <c r="I82" s="18" t="n"/>
+      <c r="J82" s="18" t="n"/>
+      <c r="K82" s="18" t="n"/>
+      <c r="L82" s="18" t="n"/>
+      <c r="M82" s="18" t="n"/>
+      <c r="N82" s="18" t="n"/>
+      <c r="O82" s="18" t="n"/>
+      <c r="P82" s="18" t="n"/>
+      <c r="Q82" s="18" t="n"/>
+      <c r="R82" s="18" t="n"/>
+      <c r="S82" s="18" t="n"/>
+      <c r="T82" s="18" t="n"/>
+      <c r="U82" s="18" t="n"/>
+      <c r="V82" s="18" t="n"/>
+      <c r="W82" s="18" t="n"/>
+      <c r="X82" s="18" t="n"/>
+      <c r="Y82" s="18" t="n"/>
+      <c r="Z82" s="18" t="n"/>
+      <c r="AA82" s="18" t="n"/>
+      <c r="AB82" s="18" t="n"/>
+      <c r="AC82" s="18" t="n"/>
+      <c r="AD82" s="18" t="n"/>
+      <c r="AE82" s="18" t="n"/>
+      <c r="AF82" s="18" t="n"/>
+      <c r="AG82" s="18" t="n"/>
+      <c r="AH82" s="18" t="n"/>
+      <c r="AI82" s="18" t="n"/>
+      <c r="AJ82" s="18" t="n"/>
+      <c r="AK82" s="18" t="n"/>
+      <c r="AL82" s="19">
+        <f>SUM(G82:AK82)</f>
+        <v/>
+      </c>
+      <c r="AM82" s="20">
+        <f>SUM(C82,AL82)</f>
+        <v/>
+      </c>
+      <c r="AN82" s="21">
+        <f>E82*AM82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="25.05" customHeight="1">
+      <c r="A83" s="36" t="inlineStr">
+        <is>
+          <t>19926</t>
+        </is>
+      </c>
+      <c r="B83" s="36" t="inlineStr">
+        <is>
+          <t>AGUA CON GAS ALUMINIO MAGMA CABREIROA C/R 50 CL</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="37" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F83" s="25">
+        <f>C83*E83</f>
+        <v/>
+      </c>
+      <c r="G83" s="18" t="n"/>
+      <c r="H83" s="18" t="n"/>
+      <c r="I83" s="18" t="n"/>
+      <c r="J83" s="18" t="n"/>
+      <c r="K83" s="18" t="n"/>
+      <c r="L83" s="18" t="n"/>
+      <c r="M83" s="18" t="n"/>
+      <c r="N83" s="18" t="n"/>
+      <c r="O83" s="18" t="n"/>
+      <c r="P83" s="18" t="n"/>
+      <c r="Q83" s="18" t="n"/>
+      <c r="R83" s="18" t="n"/>
+      <c r="S83" s="18" t="n"/>
+      <c r="T83" s="18" t="n"/>
+      <c r="U83" s="18" t="n"/>
+      <c r="V83" s="18" t="n"/>
+      <c r="W83" s="18" t="n"/>
+      <c r="X83" s="18" t="n"/>
+      <c r="Y83" s="18" t="n"/>
+      <c r="Z83" s="18" t="n"/>
+      <c r="AA83" s="18" t="n"/>
+      <c r="AB83" s="18" t="n"/>
+      <c r="AC83" s="18" t="n"/>
+      <c r="AD83" s="18" t="n"/>
+      <c r="AE83" s="18" t="n"/>
+      <c r="AF83" s="18" t="n"/>
+      <c r="AG83" s="18" t="n"/>
+      <c r="AH83" s="18" t="n"/>
+      <c r="AI83" s="18" t="n"/>
+      <c r="AJ83" s="18" t="n"/>
+      <c r="AK83" s="18" t="n"/>
+      <c r="AL83" s="19">
+        <f>SUM(G83:AK83)</f>
+        <v/>
+      </c>
+      <c r="AM83" s="20">
+        <f>SUM(C83,AL83)</f>
+        <v/>
+      </c>
+      <c r="AN83" s="21">
+        <f>E83*AM83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="25.05" customHeight="1">
+      <c r="C84" s="15">
+        <f>SUM(C7:C83)</f>
+        <v/>
+      </c>
+      <c r="E84" s="22" t="inlineStr">
         <is>
           <t>ESTOCAJE  INICIAL</t>
         </is>
       </c>
-      <c r="F79" s="23">
-        <f>SUM(F7:F78)</f>
-        <v/>
-      </c>
-      <c r="G79" s="14" t="n"/>
-      <c r="H79" s="14" t="n"/>
-      <c r="I79" s="14" t="n"/>
-      <c r="J79" s="14" t="n"/>
-      <c r="K79" s="14" t="n"/>
-      <c r="L79" s="14" t="n"/>
-      <c r="M79" s="14" t="n"/>
-      <c r="N79" s="14" t="n"/>
-      <c r="O79" s="14" t="n"/>
-      <c r="P79" s="14" t="n"/>
-      <c r="Q79" s="14" t="n"/>
-      <c r="R79" s="14" t="n"/>
-      <c r="S79" s="14" t="n"/>
-      <c r="T79" s="14" t="n"/>
-      <c r="U79" s="14" t="n"/>
-      <c r="V79" s="14" t="n"/>
-      <c r="W79" s="14" t="n"/>
-      <c r="X79" s="14" t="n"/>
-      <c r="Y79" s="14" t="n"/>
-      <c r="Z79" s="14" t="n"/>
-      <c r="AA79" s="14" t="n"/>
-      <c r="AB79" s="14" t="n"/>
-      <c r="AC79" s="14" t="n"/>
-      <c r="AD79" s="14" t="n"/>
-      <c r="AE79" s="14" t="n"/>
-      <c r="AF79" s="14" t="n"/>
-      <c r="AG79" s="14" t="n"/>
-      <c r="AH79" s="14" t="n"/>
-      <c r="AI79" s="14" t="n"/>
-      <c r="AJ79" s="14" t="n"/>
-      <c r="AK79" s="14" t="n"/>
-      <c r="AL79" s="14" t="n"/>
-      <c r="AM79" s="14">
-        <f>SUM(AM7:AM78)</f>
-        <v/>
-      </c>
-      <c r="AN79" s="24">
-        <f>SUM(AN7:AN78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" ht="25.05" customHeight="1">
-      <c r="D80" s="14" t="n"/>
-      <c r="E80" s="14" t="n"/>
-      <c r="F80" s="14" t="n"/>
-      <c r="G80" s="14" t="n"/>
-      <c r="H80" s="14" t="n"/>
-      <c r="I80" s="14" t="n"/>
-      <c r="J80" s="14" t="n"/>
-      <c r="K80" s="14" t="n"/>
-      <c r="L80" s="14" t="n"/>
-      <c r="M80" s="14" t="n"/>
-      <c r="N80" s="14" t="n"/>
-      <c r="O80" s="14" t="n"/>
-      <c r="P80" s="14" t="n"/>
-      <c r="Q80" s="14" t="n"/>
-      <c r="R80" s="14" t="n"/>
-      <c r="S80" s="14" t="n"/>
-      <c r="T80" s="14" t="n"/>
-      <c r="U80" s="14" t="n"/>
-      <c r="V80" s="14" t="n"/>
-      <c r="W80" s="14" t="n"/>
-      <c r="X80" s="14" t="n"/>
-      <c r="Y80" s="14" t="n"/>
-      <c r="Z80" s="14" t="n"/>
-      <c r="AA80" s="14" t="n"/>
-      <c r="AB80" s="14" t="n"/>
-      <c r="AC80" s="14" t="n"/>
-      <c r="AD80" s="14" t="n"/>
-      <c r="AE80" s="14" t="n"/>
-      <c r="AF80" s="14" t="n"/>
-      <c r="AG80" s="14" t="n"/>
-      <c r="AH80" s="14" t="n"/>
-      <c r="AI80" s="14" t="n"/>
-      <c r="AJ80" s="14" t="n"/>
-      <c r="AK80" s="14" t="n"/>
-      <c r="AL80" s="14" t="n"/>
-      <c r="AM80" s="14" t="n"/>
-      <c r="AN80" s="14" t="n"/>
-    </row>
-    <row r="81" ht="25.05" customHeight="1">
-      <c r="D81" s="14" t="n"/>
-      <c r="E81" s="14" t="n"/>
-      <c r="F81" s="14" t="n"/>
-      <c r="G81" s="14" t="n"/>
-      <c r="H81" s="14" t="n"/>
-      <c r="I81" s="14" t="n"/>
-      <c r="J81" s="14" t="n"/>
-      <c r="K81" s="14" t="n"/>
-      <c r="L81" s="14" t="n"/>
-      <c r="M81" s="14" t="n"/>
-      <c r="N81" s="14" t="n"/>
-      <c r="O81" s="14" t="n"/>
-      <c r="P81" s="14" t="n"/>
-      <c r="Q81" s="14" t="n"/>
-      <c r="R81" s="14" t="n"/>
-      <c r="S81" s="14" t="n"/>
-      <c r="T81" s="14" t="n"/>
-      <c r="U81" s="14" t="n"/>
-      <c r="V81" s="14" t="n"/>
-      <c r="W81" s="14" t="n"/>
-      <c r="X81" s="14" t="n"/>
-      <c r="Y81" s="14" t="n"/>
-      <c r="Z81" s="14" t="n"/>
-      <c r="AA81" s="14" t="n"/>
-      <c r="AB81" s="14" t="n"/>
-      <c r="AC81" s="14" t="n"/>
-      <c r="AD81" s="14" t="n"/>
-      <c r="AE81" s="14" t="n"/>
-      <c r="AF81" s="14" t="n"/>
-      <c r="AG81" s="14" t="n"/>
-      <c r="AH81" s="14" t="n"/>
-      <c r="AI81" s="14" t="n"/>
-      <c r="AJ81" s="14" t="n"/>
-      <c r="AK81" s="14" t="n"/>
-      <c r="AL81" s="14" t="n"/>
-      <c r="AM81" s="14" t="n"/>
-      <c r="AN81" s="14" t="n"/>
-    </row>
-    <row r="82" ht="25.05" customHeight="1">
-      <c r="D82" s="14" t="n"/>
-      <c r="E82" s="14" t="n"/>
-      <c r="F82" s="14" t="n"/>
-      <c r="G82" s="14" t="n"/>
-      <c r="H82" s="14" t="n"/>
-      <c r="I82" s="14" t="n"/>
-      <c r="J82" s="14" t="n"/>
-      <c r="K82" s="14" t="n"/>
-      <c r="L82" s="14" t="n"/>
-      <c r="M82" s="14" t="n"/>
-      <c r="N82" s="14" t="n"/>
-      <c r="O82" s="14" t="n"/>
-      <c r="P82" s="14" t="n"/>
-      <c r="Q82" s="14" t="n"/>
-      <c r="R82" s="14" t="n"/>
-      <c r="S82" s="14" t="n"/>
-      <c r="T82" s="14" t="n"/>
-      <c r="U82" s="14" t="n"/>
-      <c r="V82" s="14" t="n"/>
-      <c r="W82" s="14" t="n"/>
-      <c r="X82" s="14" t="n"/>
-      <c r="Y82" s="14" t="n"/>
-      <c r="Z82" s="14" t="n"/>
-      <c r="AA82" s="14" t="n"/>
-      <c r="AB82" s="14" t="n"/>
-      <c r="AC82" s="14" t="n"/>
-      <c r="AD82" s="14" t="n"/>
-      <c r="AE82" s="14" t="n"/>
-      <c r="AF82" s="14" t="n"/>
-      <c r="AG82" s="14" t="n"/>
-      <c r="AH82" s="14" t="n"/>
-      <c r="AI82" s="14" t="n"/>
-      <c r="AJ82" s="14" t="n"/>
-      <c r="AK82" s="14" t="n"/>
-      <c r="AL82" s="14" t="n"/>
-      <c r="AM82" s="14" t="n"/>
-      <c r="AN82" s="14" t="n"/>
-    </row>
-    <row r="83" ht="25.05" customHeight="1">
-      <c r="D83" s="14" t="n"/>
-      <c r="E83" s="14" t="n"/>
-      <c r="F83" s="14" t="n"/>
-      <c r="G83" s="14" t="n"/>
-      <c r="H83" s="14" t="n"/>
-      <c r="I83" s="14" t="n"/>
-      <c r="J83" s="14" t="n"/>
-      <c r="K83" s="14" t="n"/>
-      <c r="L83" s="14" t="n"/>
-      <c r="M83" s="14" t="n"/>
-      <c r="N83" s="14" t="n"/>
-      <c r="O83" s="14" t="n"/>
-      <c r="P83" s="14" t="n"/>
-      <c r="Q83" s="14" t="n"/>
-      <c r="R83" s="14" t="n"/>
-      <c r="S83" s="14" t="n"/>
-      <c r="T83" s="14" t="n"/>
-      <c r="U83" s="14" t="n"/>
-      <c r="V83" s="14" t="n"/>
-      <c r="W83" s="14" t="n"/>
-      <c r="X83" s="14" t="n"/>
-      <c r="Y83" s="14" t="n"/>
-      <c r="Z83" s="14" t="n"/>
-      <c r="AA83" s="14" t="n"/>
-      <c r="AB83" s="14" t="n"/>
-      <c r="AC83" s="14" t="n"/>
-      <c r="AD83" s="14" t="n"/>
-      <c r="AE83" s="14" t="n"/>
-      <c r="AF83" s="14" t="n"/>
-      <c r="AG83" s="14" t="n"/>
-      <c r="AH83" s="14" t="n"/>
-      <c r="AI83" s="14" t="n"/>
-      <c r="AJ83" s="14" t="n"/>
-      <c r="AK83" s="14" t="n"/>
-      <c r="AL83" s="14" t="n"/>
-      <c r="AM83" s="14" t="n"/>
-      <c r="AN83" s="14" t="n"/>
-    </row>
-    <row r="84" ht="25.05" customHeight="1">
-      <c r="D84" s="14" t="n"/>
-      <c r="E84" s="14" t="n"/>
-      <c r="F84" s="14" t="n"/>
+      <c r="F84" s="23">
+        <f>SUM(F7:F83)</f>
+        <v/>
+      </c>
       <c r="G84" s="14" t="n"/>
       <c r="H84" s="14" t="n"/>
       <c r="I84" s="14" t="n"/>
@@ -6331,8 +6483,14 @@
       <c r="AJ84" s="14" t="n"/>
       <c r="AK84" s="14" t="n"/>
       <c r="AL84" s="14" t="n"/>
-      <c r="AM84" s="14" t="n"/>
-      <c r="AN84" s="14" t="n"/>
+      <c r="AM84" s="14">
+        <f>SUM(AM7:AM83)</f>
+        <v/>
+      </c>
+      <c r="AN84" s="24">
+        <f>SUM(AN7:AN83)</f>
+        <v/>
+      </c>
     </row>
     <row r="85" ht="25.05" customHeight="1">
       <c r="D85" s="14" t="n"/>
@@ -7309,6 +7467,201 @@
       <c r="AM109" s="14" t="n"/>
       <c r="AN109" s="14" t="n"/>
     </row>
+    <row r="110">
+      <c r="D110" s="14" t="n"/>
+      <c r="E110" s="14" t="n"/>
+      <c r="F110" s="14" t="n"/>
+      <c r="G110" s="14" t="n"/>
+      <c r="H110" s="14" t="n"/>
+      <c r="I110" s="14" t="n"/>
+      <c r="J110" s="14" t="n"/>
+      <c r="K110" s="14" t="n"/>
+      <c r="L110" s="14" t="n"/>
+      <c r="M110" s="14" t="n"/>
+      <c r="N110" s="14" t="n"/>
+      <c r="O110" s="14" t="n"/>
+      <c r="P110" s="14" t="n"/>
+      <c r="Q110" s="14" t="n"/>
+      <c r="R110" s="14" t="n"/>
+      <c r="S110" s="14" t="n"/>
+      <c r="T110" s="14" t="n"/>
+      <c r="U110" s="14" t="n"/>
+      <c r="V110" s="14" t="n"/>
+      <c r="W110" s="14" t="n"/>
+      <c r="X110" s="14" t="n"/>
+      <c r="Y110" s="14" t="n"/>
+      <c r="Z110" s="14" t="n"/>
+      <c r="AA110" s="14" t="n"/>
+      <c r="AB110" s="14" t="n"/>
+      <c r="AC110" s="14" t="n"/>
+      <c r="AD110" s="14" t="n"/>
+      <c r="AE110" s="14" t="n"/>
+      <c r="AF110" s="14" t="n"/>
+      <c r="AG110" s="14" t="n"/>
+      <c r="AH110" s="14" t="n"/>
+      <c r="AI110" s="14" t="n"/>
+      <c r="AJ110" s="14" t="n"/>
+      <c r="AK110" s="14" t="n"/>
+      <c r="AL110" s="14" t="n"/>
+      <c r="AM110" s="14" t="n"/>
+      <c r="AN110" s="14" t="n"/>
+    </row>
+    <row r="111">
+      <c r="D111" s="14" t="n"/>
+      <c r="E111" s="14" t="n"/>
+      <c r="F111" s="14" t="n"/>
+      <c r="G111" s="14" t="n"/>
+      <c r="H111" s="14" t="n"/>
+      <c r="I111" s="14" t="n"/>
+      <c r="J111" s="14" t="n"/>
+      <c r="K111" s="14" t="n"/>
+      <c r="L111" s="14" t="n"/>
+      <c r="M111" s="14" t="n"/>
+      <c r="N111" s="14" t="n"/>
+      <c r="O111" s="14" t="n"/>
+      <c r="P111" s="14" t="n"/>
+      <c r="Q111" s="14" t="n"/>
+      <c r="R111" s="14" t="n"/>
+      <c r="S111" s="14" t="n"/>
+      <c r="T111" s="14" t="n"/>
+      <c r="U111" s="14" t="n"/>
+      <c r="V111" s="14" t="n"/>
+      <c r="W111" s="14" t="n"/>
+      <c r="X111" s="14" t="n"/>
+      <c r="Y111" s="14" t="n"/>
+      <c r="Z111" s="14" t="n"/>
+      <c r="AA111" s="14" t="n"/>
+      <c r="AB111" s="14" t="n"/>
+      <c r="AC111" s="14" t="n"/>
+      <c r="AD111" s="14" t="n"/>
+      <c r="AE111" s="14" t="n"/>
+      <c r="AF111" s="14" t="n"/>
+      <c r="AG111" s="14" t="n"/>
+      <c r="AH111" s="14" t="n"/>
+      <c r="AI111" s="14" t="n"/>
+      <c r="AJ111" s="14" t="n"/>
+      <c r="AK111" s="14" t="n"/>
+      <c r="AL111" s="14" t="n"/>
+      <c r="AM111" s="14" t="n"/>
+      <c r="AN111" s="14" t="n"/>
+    </row>
+    <row r="112">
+      <c r="D112" s="14" t="n"/>
+      <c r="E112" s="14" t="n"/>
+      <c r="F112" s="14" t="n"/>
+      <c r="G112" s="14" t="n"/>
+      <c r="H112" s="14" t="n"/>
+      <c r="I112" s="14" t="n"/>
+      <c r="J112" s="14" t="n"/>
+      <c r="K112" s="14" t="n"/>
+      <c r="L112" s="14" t="n"/>
+      <c r="M112" s="14" t="n"/>
+      <c r="N112" s="14" t="n"/>
+      <c r="O112" s="14" t="n"/>
+      <c r="P112" s="14" t="n"/>
+      <c r="Q112" s="14" t="n"/>
+      <c r="R112" s="14" t="n"/>
+      <c r="S112" s="14" t="n"/>
+      <c r="T112" s="14" t="n"/>
+      <c r="U112" s="14" t="n"/>
+      <c r="V112" s="14" t="n"/>
+      <c r="W112" s="14" t="n"/>
+      <c r="X112" s="14" t="n"/>
+      <c r="Y112" s="14" t="n"/>
+      <c r="Z112" s="14" t="n"/>
+      <c r="AA112" s="14" t="n"/>
+      <c r="AB112" s="14" t="n"/>
+      <c r="AC112" s="14" t="n"/>
+      <c r="AD112" s="14" t="n"/>
+      <c r="AE112" s="14" t="n"/>
+      <c r="AF112" s="14" t="n"/>
+      <c r="AG112" s="14" t="n"/>
+      <c r="AH112" s="14" t="n"/>
+      <c r="AI112" s="14" t="n"/>
+      <c r="AJ112" s="14" t="n"/>
+      <c r="AK112" s="14" t="n"/>
+      <c r="AL112" s="14" t="n"/>
+      <c r="AM112" s="14" t="n"/>
+      <c r="AN112" s="14" t="n"/>
+    </row>
+    <row r="113">
+      <c r="D113" s="14" t="n"/>
+      <c r="E113" s="14" t="n"/>
+      <c r="F113" s="14" t="n"/>
+      <c r="G113" s="14" t="n"/>
+      <c r="H113" s="14" t="n"/>
+      <c r="I113" s="14" t="n"/>
+      <c r="J113" s="14" t="n"/>
+      <c r="K113" s="14" t="n"/>
+      <c r="L113" s="14" t="n"/>
+      <c r="M113" s="14" t="n"/>
+      <c r="N113" s="14" t="n"/>
+      <c r="O113" s="14" t="n"/>
+      <c r="P113" s="14" t="n"/>
+      <c r="Q113" s="14" t="n"/>
+      <c r="R113" s="14" t="n"/>
+      <c r="S113" s="14" t="n"/>
+      <c r="T113" s="14" t="n"/>
+      <c r="U113" s="14" t="n"/>
+      <c r="V113" s="14" t="n"/>
+      <c r="W113" s="14" t="n"/>
+      <c r="X113" s="14" t="n"/>
+      <c r="Y113" s="14" t="n"/>
+      <c r="Z113" s="14" t="n"/>
+      <c r="AA113" s="14" t="n"/>
+      <c r="AB113" s="14" t="n"/>
+      <c r="AC113" s="14" t="n"/>
+      <c r="AD113" s="14" t="n"/>
+      <c r="AE113" s="14" t="n"/>
+      <c r="AF113" s="14" t="n"/>
+      <c r="AG113" s="14" t="n"/>
+      <c r="AH113" s="14" t="n"/>
+      <c r="AI113" s="14" t="n"/>
+      <c r="AJ113" s="14" t="n"/>
+      <c r="AK113" s="14" t="n"/>
+      <c r="AL113" s="14" t="n"/>
+      <c r="AM113" s="14" t="n"/>
+      <c r="AN113" s="14" t="n"/>
+    </row>
+    <row r="114">
+      <c r="D114" s="14" t="n"/>
+      <c r="E114" s="14" t="n"/>
+      <c r="F114" s="14" t="n"/>
+      <c r="G114" s="14" t="n"/>
+      <c r="H114" s="14" t="n"/>
+      <c r="I114" s="14" t="n"/>
+      <c r="J114" s="14" t="n"/>
+      <c r="K114" s="14" t="n"/>
+      <c r="L114" s="14" t="n"/>
+      <c r="M114" s="14" t="n"/>
+      <c r="N114" s="14" t="n"/>
+      <c r="O114" s="14" t="n"/>
+      <c r="P114" s="14" t="n"/>
+      <c r="Q114" s="14" t="n"/>
+      <c r="R114" s="14" t="n"/>
+      <c r="S114" s="14" t="n"/>
+      <c r="T114" s="14" t="n"/>
+      <c r="U114" s="14" t="n"/>
+      <c r="V114" s="14" t="n"/>
+      <c r="W114" s="14" t="n"/>
+      <c r="X114" s="14" t="n"/>
+      <c r="Y114" s="14" t="n"/>
+      <c r="Z114" s="14" t="n"/>
+      <c r="AA114" s="14" t="n"/>
+      <c r="AB114" s="14" t="n"/>
+      <c r="AC114" s="14" t="n"/>
+      <c r="AD114" s="14" t="n"/>
+      <c r="AE114" s="14" t="n"/>
+      <c r="AF114" s="14" t="n"/>
+      <c r="AG114" s="14" t="n"/>
+      <c r="AH114" s="14" t="n"/>
+      <c r="AI114" s="14" t="n"/>
+      <c r="AJ114" s="14" t="n"/>
+      <c r="AK114" s="14" t="n"/>
+      <c r="AL114" s="14" t="n"/>
+      <c r="AM114" s="14" t="n"/>
+      <c r="AN114" s="14" t="n"/>
+    </row>
   </sheetData>
   <autoFilter ref="A6:F6"/>
   <mergeCells count="3">
